--- a/Dezi Art Prize Faculty Scraping/master_faculty.xlsx
+++ b/Dezi Art Prize Faculty Scraping/master_faculty.xlsx
@@ -12,6 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UGA" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Iowa" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UT Austin" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RIT" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edinburgh" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SNU" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Temple-Tyler'!$A$7:$I$58</definedName>
@@ -19,6 +22,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UGA'!$A$7:$I$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Iowa'!$A$7:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'UT Austin'!$A$7:$I$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RIT'!$A$7:$I$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Edinburgh'!$A$7:$I$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'SNU'!$A$7:$I$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9546,4 +9552,8833 @@
   <autoFilter ref="A7:I32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I113"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: United States</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: Rochester, NY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: Rochester Institute of Technology, College of Art and Design - 20 per-program faculty directory pages (program-directory/&lt;id&gt;), IDs found via each program's official landing page rather than guessed. Covers all in-scope BFA/MFA programs (Art Education MST excluded); Furniture Design AOS, Photographic Arts Exploration, and Studio Arts Exploration have no faculty-directory link and were skipped. Medium assigned per-program (e.g. Ceramics MFA -&gt; Sculpture), not from a per-person field. Faculty cross-listed on multiple program pages (e.g. BFA + MFA in the same area) deduped, keeping the first page's medium assignment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://www.rit.edu/artdesign/program-directory/411480 (and 19 more IDs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Joey Byun</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Design</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>School of Design (3D Digital Design BFA)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>jxbfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411480</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Shaun Foster</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Professor, Design</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>School of Design (3D Digital Design BFA)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>scffaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411480</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jennifer Indovina</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Lecturer, Design</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>School of Design (3D Digital Design BFA)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>jxifaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411480</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gary Jacobs</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Associate Professor, Design</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>School of Design (3D Digital Design BFA)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>gdjfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411480</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ihab Mardini</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Associate Professor, Design</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>School of Design (3D Digital Design BFA)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ixmfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411480</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Aaron Powell</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Lecturer, Design</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>School of Design (3D Digital Design BFA)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>awpfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411480</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Philip Szrama</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Design</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>School of Design (3D Digital Design BFA)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pxsfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411480</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Amy Adrion</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>aaapph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Vashti Anderson</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vxapph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Meghdad Asadilari</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>mxafaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Christine Banna</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>cabpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kevin Bauer</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Senior Lecturer, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>kmbpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jack Beck</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Professor, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>jabpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mari Jaye Blanchard</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Associate Professor, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>mjbpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Don Casper</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>don.casper@rit.edu</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Frank Deese</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Associate Professor, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>fwdppr@rit.edu</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Jonathan Knight</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Lecturer, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>jdkpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Brian Larson</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Associate Professor, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>bjlppr@rit.edu</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Linda Moroney</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Lecturer, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>linda.moroney@rit.edu</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Peter Murphey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Principal Lecturer, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ptmpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Atia Newman</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Associate Professor, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>atia.newman@rit.edu</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Jesse O'Brien</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>jsoigm@rit.edu</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mark Reisch</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Associate Professor, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>mark.reisch@rit.edu</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Jonathan Seligson</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Senior Lecturer, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>jvspph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Dave Sluberski</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Principal Lecturer, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>dsspph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Vanessa Sweet</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Associate Professor, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>vbspph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Munjal Yagnik</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Associate Professor, Film and Animation</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>School of Film and Animation (Film and Animation BFA)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>munjal.yagnik@rit.edu</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411483</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>William Colgrove</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Design</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>School of Design (Graphic Design BFA)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>wfcfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411486</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Keli DiRisio</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Associate Professor, Design</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>School of Design (Graphic Design BFA)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>keli.dirisio@rit.edu</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411486</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Carol Fillip</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Associate Professor, Design</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>School of Design (Graphic Design BFA)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>carol.fillip@rit.edu</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411486</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lorrie Frear</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Professor, Design</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>School of Design (Graphic Design BFA)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>lorrie.frear@rit.edu</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411486</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Mitch Goldstein</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Associate Professor, Design</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>School of Design (Graphic Design BFA)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>mmgfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411486</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Anna Schum-Houck</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Adjunct</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>School of Art (Graphic Design BFA)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ashfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411486</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Allen Douglas</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Senior Lecturer, Art</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>School of Art (Illustration BFA)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>agdfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411489</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Chad Grohman</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Associate Professor, Art</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>School of Art (Illustration BFA)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>clgfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411489</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Jeff Harter</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Art</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>School of Art (Illustration BFA)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>jhfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411489</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Corinn Marriott</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Visiting Lecturer, Art</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>School of Art (Illustration BFA)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>cxmfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411489</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Alesha Williams</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Art</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>School of Art (Illustration BFA)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>aewfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411489</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Joseph Allgeier</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Visiting Lecturer, Design</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>School of Design (Industrial Design BFA)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>jrapgd@rit.edu</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411492</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Lara Cardoso Goulart</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Lecturer, Design</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>School of Design (Industrial Design BFA)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>lcfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411492</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Charles Carson</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Senior Lecturer, Design</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>School of Design (Industrial Design BFA)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>cgcfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411492</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Melissa Dawson</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Associate Professor, Design</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>School of Design (Industrial Design BFA)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>mdmfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411492</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Alex Lobos</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Director, School of Design</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Dean’s Office (Industrial Design BFA)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>alex.lobos@rit.edu</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411492</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mindy Magyar</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Associate Professor, Design</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>School of Design (Industrial Design BFA)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>mxmfaa1@rit.edu</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411492</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Juan Noguera</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Design</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>School of Design (Industrial Design BFA)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>jcnfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411492</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Josh Owen</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Vignelli Distinguished Professor of Design; Director, Vignelli Center for Design Studies</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>School of Design (Industrial Design BFA)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>jkofaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411492</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Lorianne Resch</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Lecturer, Design</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>School of Design (Industrial Design BFA)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>lmrfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411492</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Stan Rickel</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Associate Professor, Design</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>School of Design (Industrial Design BFA)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>srrfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411492</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Amos Scully</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Associate Professor, Design</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>School of Design (Industrial Design BFA)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>aasfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411492</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Marissa Tirone</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Design</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>School of Design (Industrial Design BFA)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>mxtfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411492</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Mary Golden</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Associate Professor, Design</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>School of Design (Interior Design BFA)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>megfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411495</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Kelly Jahn</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Professor of Practice, Design</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>School of Design (Interior Design BFA)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>kajfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411495</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Rachel Bajema</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Art</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>School of Art (Medical Illustration BFA)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>rxbfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411498</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Craig Foster</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Associate Professor, Art - Medical Illustration and Informatics</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>School of Art (Medical Illustration BFA)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ceffaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411498</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Alan Gesek</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Visiting Lecturer, Art</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>School of Art (Medical Illustration BFA)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>afgfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411498</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>James Perkins</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Professor and Program Director, Medical Illustration</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Department of Medical Sciences, Health, and Management (Medical Illustration BFA)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>japfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411498</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Jason Arena</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Associate Professor, Design</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>School of Design (New Media Design BFA)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>jxafaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411504</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Mike Minerva</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Professor of Practice, Design</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>School of Design (New Media Design BFA)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>mbmfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411504</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Hye-Jin Nae</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Associate Professor, Design</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>School of Design (New Media Design BFA)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>hxnfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411504</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Joel Rosen</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Lecturer, Design</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>School of Design (New Media Design BFA)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>jarfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411504</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Adam Smith</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Associate Professor, Design</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>School of Design (New Media Design BFA)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>aesfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411504</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Mike Strobert</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Senior Lecturer, Design</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>School of Design (New Media Design BFA)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>mpsfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411504</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Melissa Warp</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Senior Lecturer, Design</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>School of Design (New Media Design BFA)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>mlwfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411504</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Emily Baker</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Adjunct</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>eabpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Kristy Boyce</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>klbpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Meredith Davenport</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Associate Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>mldpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Rachel Jerome Ferraro</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Associate Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>rjfpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Gregory Halpern</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>grhpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Greg Hayes</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Lecturer, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>gjhpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Rachel Hutcheson</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Visiting Assistant Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>rlhpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Susan Lakin</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Dean’s Office (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>srlpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Clay Patrick McBride</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Assistant Professor and Dr. Ronald Francis/Mabel Francis Professor</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>cpmcbpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Joshua Rashaad McFadden</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>jrmpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Josh Meltzer</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Associate Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>jhmpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Laurie O Brien</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Associate Professor and James E McGhee Fellow</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>lcofaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Juan Orrantia</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>jcopph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Ahndraya Parlato</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>adppph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Jenn Poggi</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Associate Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>jappph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Jim Porto</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>jppph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>William Snyder</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>wdspph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Joshua Thorson</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Associate Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>jjtpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Carole Woodlock</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>cmwfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Catherine Zuromskis</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic and Imaging Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>czpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411507</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Daniel Hughes</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Lecturer, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic Sciences BS)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>dahpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411510</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ted Kinsman</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Associate Professor, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic Sciences BS)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>emkpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411510</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Nanette Salvaggio</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Lecturer, Photo Arts and Sciences</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>School of Photographic Arts and Sciences (Photographic Sciences BS)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>nlspph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411510</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Christye Sisson</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Director, School of Photographic Arts and Sciences; Gannett Endowed Professor</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Dean’s Office (Photographic Sciences BS)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>cpspph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411510</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Andy Buck</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Professor, American Crafts</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>School for American Crafts (Studio Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>aabsac@rit.edu</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411513</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Juan Carlos Caballero-Perez</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Professor, American Crafts</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>School for American Crafts (Studio Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>jcc2390@rit.edu</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411513</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Denton Crawford</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Senior Lecturer, Art</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>School of Art (Studio Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>denton@rit.edu</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411513</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Laurel Fulton</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Assistant Professor, American Crafts</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>School for American Crafts (Studio Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>lnffaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411513</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Emily Glass</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Principal Lecturer, Art</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>School of Art (Studio Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>elgfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411513</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Rolf Hoeg</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Lecturer, Art</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>School of Art (Studio Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>rehsac@rit.edu</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411513</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Elizabeth Kronfield</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Director, School for American Crafts and School of Art</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Dean’s Office (Studio Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>edkfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411513</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Amy McLaren</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Senior Lecturer, Art</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>School of Art (Studio Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>alwfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411513</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Suzanne Peck</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Lecturer, Art</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>School of Art (Studio Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>smpfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411513</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Peter Pincus</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Associate Professor, Art</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>School for American Crafts (Studio Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>pjpsac@rit.edu</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411513</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>David Schnuckel</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Associate Professor and Charlotte Mowris Fellow</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>School for American Crafts (Studio Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>dassac@rit.edu</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411513</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Jane Shellenbarger</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Professor and Ann Mowris Mulligan Endowed Professor</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>School for American Crafts (Studio Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>jmssac@rit.edu</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411513</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Luvon Sheppard</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Professor, Art</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>School of Art (Studio Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>lxsfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411513</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Clifford Wun</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Associate Professor, Art</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>School of Art (Studio Arts BFA)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>clwfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411513</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Christopher Lyons</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Adjunct</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>School of Design (Industrial Design MFA)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>cjlfaaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411390</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Peter Byrne</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Professor, Design</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>School of Design (Visual Communication Design MFA)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>pjbfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411396</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Daniel DeLuna</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Associate Professor, Design</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>School of Design (Visual Communication Design MFA)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>dxdpph@rit.edu</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411396</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Joyce Hertzson</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Professor, Design</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>School of Design (Visual Communication Design MFA)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>jshfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411396</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology, College of Art and Design</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>A Jordan</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Design</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>School of Design (Visual Communication Design MFA)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>axjfaa@rit.edu</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://www.rit.edu/artdesign/program-directory/411396</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I113"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: Edinburgh, Scotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: Edinburgh College of Art, University of Edinburgh - /people directory filtered server-side to Academic Staff + Key Academic Office Holders only (excludes Honorary/Emeritus, Postgraduate Research Students, Professional Services, Student Representation), 13 pages. Medium classified from the role/title text shown directly on each card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=0 (through page=12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Natalie Adamson-Wain</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Teaching Fellow - Design (Textiles) MA, RCA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Teaching Fellow - Design (Textiles) MA, RCA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nadamson@exseed.ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Megan Baker</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Programme Director, Performance Costume</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Programme Director, Performance Costume</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>megan.baker@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Scott Barley</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Teaching Fellow in Film Directing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Teaching Fellow in Film Directing</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>sbarley@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Yorgos Berdos</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Teaching Fellow, Computational Design &amp; Visualisaion</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Teaching Fellow, Computational Design &amp; Visualisaion</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yorgos.berdos@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Katie Braid</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Teaching Fellow Fashion Illustration and Portfolio</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Teaching Fellow Fashion Illustration and Portfolio</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>kbraid2@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alison Claire Brown</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Teaching Fellow in Performance Costume</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Teaching Fellow in Performance Costume</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>abrown35@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gemma Brown</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Teaching Fellow, Textiles, School of Design</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Teaching Fellow, Textiles, School of Design</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>gemma.brown@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dan Castro</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lecturer in Animation</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lecturer in Animation</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>dcastro@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=2</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dr Jamie Chambers</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Senior Lecturer in Film</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Senior Lecturer in Film</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>jamie.chambers@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=2</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Susan Cross</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Reader, Jewellery and Silversmithing</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Reader, Jewellery and Silversmithing</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>s.cross@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=2</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Professor Emma Davie</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Personal Chair of Documentary Film</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Personal Chair of Documentary Film</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>e.davie@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=2</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dr Nichola Dobson</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Senior Lecturer in Animation</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Senior Lecturer in Animation</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>n.dobson@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=3</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Claire Ferguson</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Lecturer, Fashion, School of Design</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Lecturer, Fashion, School of Design</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>c.ferguson@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=3</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Emily Ford-Halliday</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Lecturer, Fashion Design, School of Design</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lecturer, Fashion Design, School of Design</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emily.ford-halliday@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=4</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kirsty Frew</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SCF Lecturer in Fashion Innovation</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SCF Lecturer in Fashion Innovation</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>kirsty.frew@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=4</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Silvia Garcia</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Programme Director, SCF Fashion Interior Design</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Programme Director, SCF Fashion Interior Design</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>silvia.ojedagarcia@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=4</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pilar Garcia de Leaniz Rodriguez</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Lecturer in Design (Illustration, Textiles and Performance Costume)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Lecturer in Design (Illustration, Textiles and Performance Costume)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>pgarcia@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=4</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Anika Hoppel</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Programme Director, SCF Fashion Innovation</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Programme Director, SCF Fashion Innovation</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>anika.hoppel@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=5</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Professor Mal James</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Personal Chair of Fashion Design</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Personal Chair of Fashion Design</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>mal.james@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=6</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Mirka Janeckova</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Teaching Fellow in Jewellery and Silversmithing</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Teaching Fellow in Jewellery and Silversmithing</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>mirka.janeckova@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=6</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Dr Jessamy Kelly</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Senior Lecturer in Glass and Ceramics</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Senior Lecturer in Glass and Ceramics</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Jessamy.kelly@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=6</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ling Lee</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Lecturer in Film and Moving Image</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Lecturer in Film and Moving Image</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ling.lee@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=6</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Colleen Leitch</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Lecturer, SCF Fashion Innovation</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lecturer, SCF Fashion Innovation</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>cleitch3@exseed.ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=6</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>David Lemm</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Lecturer in Graphic Design</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lecturer in Graphic Design</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>dlemm2@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=7</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Dr Xuechang Leng</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Lecturer, SCF Fashion Interior Design</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Lecturer, SCF Fashion Interior Design</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>xleng@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=7</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Orlando Lloyd</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Lecturer in Graphic Design</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Lecturer in Graphic Design</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>o.lloyd@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=7</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Professor Juliette MacDonald</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chair of Craft History and Theory</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Chair of Craft History and Theory</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>juliette.macdonald@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=7</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Dr Maria Maclennan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Senior Lecturer (Teaching and Research) in Jewellery and Silversmithing</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Senior Lecturer (Teaching and Research) in Jewellery and Silversmithing</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>maria.maclennan@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=7</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Alan Mason</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Lecturer, Animation</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lecturer, Animation</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>alan.mason@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=7</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Isla Munro</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Lecturer, Product Design</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Lecturer, Product Design</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>isla.munro@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=8</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Dr Jonathan Murray</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Personal Chair of Film Theory, History and Criticism</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Personal Chair of Film Theory, History and Criticism</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>jonny.murray@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=8</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Dr Alex Nevill</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Lecturer in Film and Moving Image</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Lecturer in Film and Moving Image</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>anevill@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=8</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Dr Bettina Nissen</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Lecturer in Interaction Design</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Lecturer in Interaction Design</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>bettina.nissen@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=8</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Will Nolan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Lecturer, SCF Fashion Interior Design</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Lecturer, SCF Fashion Interior Design</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>wnolan@exseed.ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=9</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Dr Denitsa Petrova</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Lecturer In Digital Design</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Lecturer In Digital Design</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Denitsa.Petrova@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=9</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sally Ann Provan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Teaching Fellow, Fashion, School of Design</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Teaching Fellow, Fashion, School of Design</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>s.provan@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=9</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Dr Jules Rawlinson</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Senior Lecturer, Digital Design</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Senior Lecturer, Digital Design</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Jules.Rawlinson@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=10</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Emma Joanne Renhard</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Lecturer, Performance Costume, School of Design</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Lecturer, Performance Costume, School of Design</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>erenhard@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=10</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ewan Robertson</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Lecturer, Sculpture</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Lecturer, Sculpture</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>e.robertson@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=10</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Marco Scerri</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Teaching Fellow, Graphic Design, School of Design</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Teaching Fellow, Graphic Design, School of Design</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>m.scerri@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=10</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Donald Soutar</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Teaching Fellow in Graphic Design</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Teaching Fellow in Graphic Design</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>dsoutar@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=11</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Richard Thompson</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Teaching Fellow in Product Design</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Teaching Fellow in Product Design</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>rthomps5@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=11</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Elena Tsyplakova</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Teaching Fellow, Fashion, School of Design</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Teaching Fellow, Fashion, School of Design</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>elena.tsyplakova@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=11</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Edinburgh College of Art, University of Edinburgh</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Dr Patricia Wu Wu</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Lecturer in Fashion Design</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Lecturer in Fashion Design</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>pwuwu@ed.ac.uk</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.eca.ed.ac.uk/people?field_people_type_target_id%5B17%5D=17&amp;field_people_type_target_id%5B16%5D=16&amp;page=12</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I51"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: South Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: Seoul</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: Seoul National University, College of Fine Arts - 5 per-department faculty pages (Design, Painting, Sculpture, Craft, Oriental Painting). JS-rendered - required crawl4ai. Medium classified from each person's research-area text, falling back to the department itself when the area text has no medium keyword (e.g. 'Theory of Art').</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://art.snu.ac.kr/en/category/design-en/?catemenu=Faculty&amp;type=major (and 4 more department category pages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ahn, Seongmo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Chair of the Department of Design</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Design - Spatial Design, Parametric Design, Digital Environment</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>sm.ahn@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/design-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lee Jang sub</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Design - Public Communication, Branding</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>leejangsub@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/design-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Park, Young-mog</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Design - Product Design, User Interface Design</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>parkym@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/design-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Eune, Juhyun</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Design - Interaction, UX Design</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>jheune@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/design-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kymn Kyungsun</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Design - Graphic Design, Typography Design</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ks1@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/design-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jang, Sung Yun</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chair of the Department of Design and Craft</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Design - Living Design</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>jang7047@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/design-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hamamoto, Chris</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Design - Graphic Design, Computational Design</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>chamamoto@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/design-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bae Jae hyuck</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Design - Advanced Technology Convergent Design, Interaction Design</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>jaehyuck@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/design-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Shin, Chung-hoon</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chair of the Department of Painting, Chair of the Art Management Program</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Painting - Art History, Theory of Art</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>chshin31@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/painting-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kim, Hyung-Gwan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Painting - Painting</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>guan70@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/painting-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Yim, Ja-Hyuk</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Painting - Painting, Printmaking</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>jahyuk@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/painting-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Oh, Inhwan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Painting - Combined Media</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ihoh@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/painting-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kim, Jeong Han</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Painting - Convergence: Media Art and Cognitive Science</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>jeonghan@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/painting-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Yoon, Hyewon</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Painting - Art History</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>hyewon.hyewon@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/painting-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Park, Kwantaeck</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Painting - Drawing, Combined Media</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>sianiz02@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/painting-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Choi, Youngbin</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Painting - Painting</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>mjlove84@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/painting-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kim, Minae</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chair of the Department of Sculpture</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sculpture - Sculpture, Fine Art</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ilsaok1@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/sculpture-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kwon, Dae-hun</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sculpture - Sculpture</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>neo3dart@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/sculpture-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Lee, Jong-geon</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sculpture - Sculpture</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>jonggeonlee@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/sculpture-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Park, Je-sung (Je Baak)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Associate Dean, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sculpture - Installation, Art&amp;Technology</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>jebaak@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/sculpture-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Shim, Sang-yong</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sculpture - Art History</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>syshim61@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/sculpture-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Hoyeon Kang</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sculpture - Sculpture, Installation</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>rkdgh12@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/sculpture-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Han Jeong-yong</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chair of the Department of Craft</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Craft - Ceramics</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>sae0002@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/craft-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Paik, Kyung-chan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Craft - Metalwork and Jewelry</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>worker@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/craft-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Her, Boyoon</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Craft - Craft Theory</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>byher@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/craft-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Min, Bog Ki</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Craft - Jewelry</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>bezalell@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/craft-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Shin, Jakyung</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Craft - Metalwork and Jewelry</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>metal00@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/craft-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Choi, Seok-won</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Chair of the Department of Oriental Painting</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Oriental Painting - Theory of Art</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>luvnomad@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/oriental-painting-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Kim, Hyungsook</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chair of the Fine Arts Education</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Oriental Painting - Art Education &amp; Modern Art Criticism</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>kimhys@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/oriental-painting-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Kim, Seongheui</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Oriental Painting - Oriental Painting &amp; Art History</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>hemyeong@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/oriental-painting-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Shin, Hasoon</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Oriental Painting - Oriental Painting</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>shsfs@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/oriental-painting-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cho Inho</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Associate Dean(academic Affairs)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Oriental Painting - Oriental Painting</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>joint77@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/oriental-painting-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Seoul National University, College of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Jung, Haena</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Oriental Painting - Oriental Painting</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>haenajung@snu.ac.kr</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://art.snu.ac.kr/en/category/oriental-painting-en/?catemenu=Faculty&amp;type=major</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I40"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Dezi Art Prize Faculty Scraping/master_faculty.xlsx
+++ b/Dezi Art Prize Faculty Scraping/master_faculty.xlsx
@@ -15,6 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RIT" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edinburgh" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SNU" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VCU" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NID Ahmedabad" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jamia Millia Islamia" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UIC" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Temple-Tyler'!$A$7:$I$58</definedName>
@@ -25,6 +29,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RIT'!$A$7:$I$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Edinburgh'!$A$7:$I$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'SNU'!$A$7:$I$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'VCU'!$A$7:$I$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'NID Ahmedabad'!$A$7:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Jamia Millia Islamia'!$A$7:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'UIC'!$A$7:$I$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2938,6 +2946,1552 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: India</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: Ahmedabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: National Institute of Design, Ahmedabad - /people/faculty page. NOTE: this page has no pagination and lists only 9 faculty total (Industrial Design, Textile &amp; Apparel Design, Communication Design) - Ceramic/Glass and Film/Animation faculty mentioned in the research brief were NOT found; confirmed via the site's own academic program pages that Ceramic and Glass Design and Animation Film Design are not current B.Des specializations at this campus (may exist at a different NID campus, or may have been discontinued/restructured). This may be the complete current roster shown on the public site, not a scraper gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://www.nid.ac.in/people/faculty</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>National Institute of Design (NID), Ahmedabad</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mr. Ram Mattegunta</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Associate Senior Faculty, Textile &amp; Apparel Design, Vice-Chair &amp; Officiating Activity Chairperson (Education), Head-International &amp; Collaborative Programmes, Centre for Indian Craft, Coordinator - Convergence, Coordinator - Foundation Programme</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Associate Senior Faculty, Textile &amp; Apparel Design</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ram@nid.ac.in</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.nid.ac.in/people/faculty</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>National Institute of Design (NID), Ahmedabad</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ms. Archana</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Faculty, Industrial Design, Discipline Lead In-Charge(I/C) - Industrial Design, Co-coordinator - Industry Interface, Alumni Affairs &amp; Placement Cell</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Faculty, Industrial Design</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>archana@nid.ac.in</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.nid.ac.in/people/faculty</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>National Institute of Design (NID), Ahmedabad</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mr. Arnab Senapati</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Associate Senior Faculty, Textile &amp; Apparel Design, Discipline Lead - Textile &amp; Apparel Design, Head - Outreach Programmes</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Associate Senior Faculty, Textile &amp; Apparel Design</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>arnab@nid.ac.in</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.nid.ac.in/people/faculty</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>National Institute of Design (NID), Ahmedabad</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mr. Kurma Nadham</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Faculty | Discipline Lead In-Charge(I/C) - Communication Design, Coordinator - NID Press | Communication &amp; Media Cell, Coordinator - Graduation Projects</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Faculty | Discipline Lead In-Charge(I/C) - Communication Design</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>kurmanadham@nid.ac.in</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.nid.ac.in/people/faculty</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>National Institute of Design (NID), Ahmedabad</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dr. Amaltas Khan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Associate Senior Faculty, Industrial Design, Coordinator - Research &amp; Publications, Vice-Chair &amp; Officiating Activity Chairperson (IDS), Head - Design Consultancy Services</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Associate Senior Faculty, Industrial Design</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>amaltas@nid.ac.in</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.nid.ac.in/people/faculty</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>National Institute of Design (NID), Ahmedabad</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mr. Bhoomaiah Bandi</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Associate Senior Designer, Textile &amp; Apparel Design, Deputy Registrar In-Charge(I/C)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Associate Senior Designer, Textile &amp; Apparel Design</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>bhoomaiah@nid.ac.in</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.nid.ac.in/people/faculty</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>National Institute of Design (NID), Ahmedabad</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mr. Ashish Ramdas Thulkar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Senior Technical Instructor, Coordinator, Industrial Design Workshop, Coordinator - Intellectual Property Rights (IPR) Cell</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Senior Technical Instructor</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ashish@nid.ac.in</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.nid.ac.in/people/faculty</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>National Institute of Design (NID), Ahmedabad</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ms. Swati Pandey</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Faculty, Foundation Program, Academic Associate (Education), Coordinator, Textile &amp; Apparel Design Workshop</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Faculty, Foundation Program</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>swati@nid.ac.in</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.nid.ac.in/people/faculty</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: India</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: New Delhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: Jamia Millia Islamia, Faculty of Fine Arts - per-department 'Faculty Members' pages (Painting, Sculpture, Applied Art). These pages are JS-driven search widgets that return no static data on a plain fetch, but auto-load that department's own roster by default when rendered - required crawl4ai. The university-wide faculty search and the FFA-level staff search page do NOT auto-load results and were not usable. Art Education and Art History departments excluded (out of scope); Graphic Art department not attempted this pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://jmi.ac.in/ACADEMICS/Departments/Department-Of-Painting/Faculty-Members (and Department-Of-Sculpture, Department-Of-Applied-Art)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jamia Millia Islamia, Faculty of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mr. Shah Abul Faiz</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Painting</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>sfaiz@jmi.ac.in</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://jmi.ac.in/ACADEMICS/Departments/Department-Of-Painting/Faculty-Members</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jamia Millia Islamia, Faculty of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mr. Kaushal Kumar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Painting</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>kkumar@jmi.ac.in</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://jmi.ac.in/ACADEMICS/Departments/Department-Of-Painting/Faculty-Members</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jamia Millia Islamia, Faculty of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ms. Moeen Fatma</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Painting</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>mfatma@jmi.ac.in</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://jmi.ac.in/ACADEMICS/Departments/Department-Of-Painting/Faculty-Members</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jamia Millia Islamia, Faculty of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Prof. Bindulika Sharma</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>bsharma2@jmi.ac.in</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://jmi.ac.in/ACADEMICS/Departments/Department-Of-Sculpture/Faculty-Members</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Jamia Millia Islamia, Faculty of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mr. Hafeez Ahmed</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Applied Art</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>hahmed@jmi.ac.in</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://jmi.ac.in/ACADEMICS/Departments/Department-Of-Applied-Art/Faculty-Members</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Jamia Millia Islamia, Faculty of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dr. Bhupesh Chandra Little</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Applied Art</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>blittle@jmi.ac.in</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://jmi.ac.in/ACADEMICS/Departments/Department-Of-Applied-Art/Faculty-Members</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jamia Millia Islamia, Faculty of Fine Arts</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ms. Deeba Qureshi</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Applied Art</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>dqureshi1@jmi.ac.in</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://jmi.ac.in/ACADEMICS/Departments/Department-Of-Applied-Art/Faculty-Members</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: United States</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: Chicago, IL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: University of Illinois Chicago, School of Art and Art History - /content/art-faculty studio listing page (Art History faculty excluded per user's medium scope), split into sections (Studio Arts, Photography, New Media Arts, Moving Image, Interdisciplinary Degree in the Arts; Art Education section excluded). Names link to individual profile pages where email is the only place it's published - required a profile click-through pass, same pattern as Ohio State. Emeriti section has no profile links at all (plain text names only) and could not be scraped this way - skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://artandarthistory.uic.edu/content/art-faculty (plus 13 individual /profile/&lt;slug&gt; pages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago, School of Art and Art History</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dianna Frid</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Studio Arts</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>dfrid1@uic.edu</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>http://artandarthistory.uic.edu/profile/dianna-frid</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago, School of Art and Art History</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Faheem Majeed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Director of Undergraduate Studies (Art)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Studio Arts</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>fmajee2@uic.edu</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://artandarthistory.uic.edu/profile/faheem</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago, School of Art and Art History</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Matthew Metzger</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Associate Professor; Chair, Department of Art</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Studio Arts</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>matmetz@uic.edu</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>http://artandarthistory.uic.edu/profile/matthew-john-metzger</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago, School of Art and Art History</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dan Peterman</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Studio Arts</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ptrmn@uic.edu</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>http://artandarthistory.uic.edu/profile/dan-peterman</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago, School of Art and Art History</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Laurie Jo Reynolds</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Associate Professor, Social Justice and Human Rights Cluster</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Studio Arts</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ljr@uic.edu</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>http://artandarthistory.uic.edu/profile/laurie-jo-reynolds</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago, School of Art and Art History</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nate Young</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Director of Graduate Studies (Art)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Studio Arts</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>njyoung@uic.edu</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://artandarthistory.uic.edu/profile/nathaniel-young</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago, School of Art and Art History</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Beate Geissler</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>beate@uic.edu</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>http://artandarthistory.uic.edu/profile/beate-geissler</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago, School of Art and Art History</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Silvia Malagrino</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>libraes@uic.edu</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>http://artandarthistory.uic.edu/profile/silvia-malagrino</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago, School of Art and Art History</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sabrina Raaf</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New Media Arts</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>sraaf1@uic.edu</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>http://artandarthistory.uic.edu/profile/sabrina-kay-raaf</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago, School of Art and Art History</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Jennifer Reeder</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Moving Image</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>reederj@uic.edu</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>http://artandarthistory.uic.edu/profile/jennifer-k-reeder</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>University of Illinois Chicago, School of Art and Art History</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Deborah Stratman</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Moving Image</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>dstrat1@uic.edu</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>http://artandarthistory.uic.edu/profile/deborah-stratman</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I18"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -18381,4 +19935,3778 @@
   <autoFilter ref="A7:I40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: United States</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: Richmond, VA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: Virginia Commonwealth University, School of the Arts (VCUarts) - shared /directory/ filtered per-department via query param, 8 in-scope departments (Painting + Printmaking, Kinetic Imaging, Sculpture + Extended Media, Photography + Film, Communication Arts, Graphic Design, Craft and Material Studies, Fashion Design and Merchandising). Department pages mix teaching faculty with administrative/support staff under the same listing; rows with a clearly non-teaching title (Coordinator, Administrative, Manager, Technician, Advisor) were excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://arts.vcu.edu/directory/?department%5B%5D=painting-printmaking (and 7 more department query values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Peter Baldes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Painting + Printmaking</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>pjbaldes@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=painting-printmaking</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cara Benedetto</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Painting + Printmaking</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>cbenedetto@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=painting-printmaking</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jacob Broussard</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Painting + Printmaking</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>broussardjt@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=painting-printmaking</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kamryn Gillham</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Digital Content Creative</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Painting + Printmaking</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>gillhamkl@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=painting-printmaking</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Brooke Inman</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Instructor</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Painting + Printmaking</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>inmanba@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=painting-printmaking</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Holly Morrison</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Graduate Program Director</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Painting + Printmaking</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>hjmorrison@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=painting-printmaking</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Andrew Norris</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Adjunct Professor</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Painting + Printmaking</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>norrisa@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=painting-printmaking</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Noah Simblist</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Painting + Printmaking</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>nsimblist@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=painting-printmaking</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hilary Wilder</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Painting + Printmaking</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>hwilder@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=painting-printmaking</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lindsey Arturo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Adjunct Professor</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Kinetic Imaging</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>arturol@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=kinetic-imaging</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Steve Ashby</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Adjunct Professor</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Kinetic Imaging</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ashbysj@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=kinetic-imaging</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sara Bouchard</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Kinetic Imaging</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>bouchardse@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=kinetic-imaging</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Shawn Brixey</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Kinetic Imaging</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>brixey@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=kinetic-imaging</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jared Duesterhaus</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Adjunct Faculty</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Kinetic Imaging</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>duesterhausj@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=kinetic-imaging</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Marcus Fischer</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Affiliate Faculty</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Kinetic Imaging</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>fischerm2@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=kinetic-imaging</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rebecca Gates</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Affiliate Faculty</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Kinetic Imaging</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>rdgates@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=kinetic-imaging</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Hope Ginsburg</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Kinetic Imaging</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>hqginsburg@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=kinetic-imaging</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Julie Grosche</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Adjunct Professor</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Kinetic Imaging</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2D/3D Animation</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>jgroschemckea@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=kinetic-imaging</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Terry Brown</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sculpture + Extended Media</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>tlbrown2@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=sculpture-extended-media</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Jesse Burrowes</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sculpture + Extended Media</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>jhburrowes@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=sculpture-extended-media</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kendall Buster</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Graduate Director, Sculpture + Extended Media</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sculpture + Extended Media</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>kbuster@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=sculpture-extended-media</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kristin Caskey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sculpture + Extended Media</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>kacaskey@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=sculpture-extended-media</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Lily Cox-Richard</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sculpture + Extended Media</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>coxrichardlj@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=sculpture-extended-media</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Corin Hewitt</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sculpture + Extended Media</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>chewitt@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=sculpture-extended-media</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kayla Jones</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sculpture + Extended Media</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>joneskr11@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=sculpture-extended-media</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Michael Jones McKean</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sculpture + Extended Media</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>mjmckean@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=sculpture-extended-media</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Massa Lemu</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sculpture + Extended Media</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>mmlemu@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=sculpture-extended-media</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Jalen Adams</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Instructor/Adjunct Faculty</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Photography + Film</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>adamsj15@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=photography-film</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Mark Boulos</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Photography + Film</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>mboulos@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=photography-film</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Clara DeWeese</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Graduate Instructor</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Photography + Film</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>claradeweese720@gmail.com</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=photography-film</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>John D. Freyer</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Photography + Film</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>jdfreyer@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=photography-film</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Brice Goldberg</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Instructor/Adjunct Faculty</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Photography + Film</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>goldbergb@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=photography-film</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>David Guarnizo</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Instructor/Adjunct Faculty</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Photography + Film</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>guarnizode@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=photography-film</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sonali Gulati</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Professor - School of the Arts</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Photography + Film</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>sgulati@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=photography-film</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Jesse Hoyle</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Instructor/Adjunct Faculty</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Photography + Film</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>hoylejd2@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=photography-film</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Catie Leonard</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Graduate Instructor</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Photography + Film</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>leonardcj3@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=photography-film</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Jiayi Liang</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Graduate Instructor</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Photography + Film</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>liangj6@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=photography-film</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Stephen Alcorn</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>sjalcorn@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=communication-arts</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Kelly Alder</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>kpalder@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=communication-arts</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Dennis Balk</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>balkd@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=communication-arts</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Jason Bennett</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Chair, Communication Arts</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>jebennett@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=communication-arts</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Phillip Bowles</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Adjunct Professor</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>bowlespm@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=communication-arts</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Miguel Carter-Fisher</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>carterfishem@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=communication-arts</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Dorian Cohen</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>jonesd16@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=communication-arts</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Andrew Davies</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ardavies@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=communication-arts</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TyRuben Ellingson</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Associate Professor, Communication Arts</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>tellingson@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=communication-arts</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Tirazheh Eslami</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Communication Arts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>eslamit@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=communication-arts</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Herdimas Anggara</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Graphic Design</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>anggarah@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=graphic-design</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Rasim Bayramov</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Graphic Design</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>bayramovr@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=graphic-design</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Laura Chessin</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Graphic Design</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>lchessin@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=graphic-design</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Luiza Dale</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Graphic Design</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>oliveiramal@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=graphic-design</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Rosen Eveleigh</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Graphic Design</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>eveleighr@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=graphic-design</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HH Hiaasen</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Graphic Design</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>hiaasenh@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=graphic-design</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Steven Hoskins</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Graphic Design</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>slhoskins@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=graphic-design</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Mariah Barden Jones</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Graphic Design</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>mbjones2@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=graphic-design</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Aya Khalife</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Graphic Design</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>khalifea@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=graphic-design</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>nicole killian</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Graduate Director, Graphic Design</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Graphic Design</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>nmkillian@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=graphic-design</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Angela Lockhart</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Graphic Design</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>lockhartar@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=graphic-design</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Gerardo Ismael Madera</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Designer-in-Residence</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Graphic Design</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>maderag@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=graphic-design</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Elissa Armstrong</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Craft and Material Studies</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ecarmstrong@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=craft-material-studies</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Hillary Waters Fayle</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Craft and Material Studies</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>faylehw@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=craft-material-studies</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Susie Ganch</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Craft and Material Studies</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>seganch@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=craft-material-studies</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Jason Hackett</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Craft and Material Studies</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>hackettja@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=craft-material-studies</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Sarah Irvin</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Curator of Student Exhibitions and Programs</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Craft and Material Studies</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>seirvin@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=craft-material-studies</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Shannon Kurzyniec</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Post-Master's Teaching Fellow</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Craft and Material Studies</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>kurzyniecs@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=craft-material-studies</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Jaydan Moore</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Adjunct Instructor</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Craft and Material Studies</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>jtmoore2@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=craft-material-studies</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Cynthia Myron</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Senior Director of Fine Arts</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Craft and Material Studies</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>myroncj@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=craft-material-studies</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Sarah Parker</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Adjunct Faculty - Metals &amp; Jewelry</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Craft and Material Studies</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>parkers5@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=craft-material-studies</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deidra Arrington</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Fashion Design and Merchandising</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>dwarrington@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=fashion-design-merchandising</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Jennie Cook</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Fashion Design and Merchandising</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>cookjl@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=fashion-design-merchandising</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tammy Davis</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Adjunct Professor</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Fashion Design and Merchandising</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ttdavis@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=fashion-design-merchandising</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Jeannine Diego</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Fashion Design and Merchandising</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>diegoj@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=fashion-design-merchandising</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Kimberly Guthrie</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Chair, Fashion Design + Merchandising</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Fashion Design and Merchandising</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>kguthri1@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=fashion-design-merchandising</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Jarvis Jefferson</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Fashion Design and Merchandising</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>jwjefferson@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=fashion-design-merchandising</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Renee Lamb</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Fashion Design and Merchandising</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>rslamb@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=fashion-design-merchandising</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Cate Latham</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Fashion Design and Merchandising</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>lathamcc@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=fashion-design-merchandising</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Rudy Lopez</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Fashion Design and Merchandising</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>lopezr@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=fashion-design-merchandising</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Virginia Commonwealth University, School of the Arts (VCUarts)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Jackie Mullins</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Fashion Design and Merchandising</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>mullinsjf@vcu.edu</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://arts.vcu.edu/directory/?department%5B%5D=fashion-design-merchandising</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I85"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Dezi Art Prize Faculty Scraping/master_faculty.xlsx
+++ b/Dezi Art Prize Faculty Scraping/master_faculty.xlsx
@@ -19,6 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NID Ahmedabad" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jamia Millia Islamia" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UIC" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutgers" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cornell" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Temple-Tyler'!$A$7:$I$58</definedName>
@@ -33,6 +35,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'NID Ahmedabad'!$A$7:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Jamia Millia Islamia'!$A$7:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'UIC'!$A$7:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Rutgers'!$A$7:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Cornell'!$A$7:$I$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4492,6 +4496,1914 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: United States</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: New Brunswick, NJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: Rutgers University, Mason Gross School of the Arts - Art &amp; Design department faculty/staff page. Emails ARE visible directly on the listing (better than the research brief's Tier 2 classification implied) - no profile click-through needed. Only faculty whose title text names a specific medium were kept (e.g. 'Associate Professor in Photography'); generic titles ('Professor') with no medium signal were left out rather than guessed, since this page has no separate discipline field. One email format quirk: a few hrefs are 'mailto:Name &lt;email&gt;' URL-encoded rather than a bare address - the actual address was extracted from either form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://www.masongross.rutgers.edu/degrees-programs/art-design/faculty-staff/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Rutgers University, Mason Gross School of the Arts</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jacqueline Thaw</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Chair Associate Professor in Design</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Art &amp; Design</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>thaw@mgsa.rutgers.edu</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.masongross.rutgers.edu/degrees-programs/art-design/faculty-staff/</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rutgers University, Mason Gross School of the Arts</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Atif Akin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MFA in Design Director Professor</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Art &amp; Design</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>aakin@mgsa.rutgers.edu</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.masongross.rutgers.edu/degrees-programs/art-design/faculty-staff/</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rutgers University, Mason Gross School of the Arts</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Miranda Lichtenstein</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Associate Professor in Photography</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Art &amp; Design</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>mlichtenstein@mgsa.rutgers.edu</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.masongross.rutgers.edu/degrees-programs/art-design/faculty-staff/</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rutgers University, Mason Gross School of the Arts</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Barbara Madsen</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Director of the Rutgers Printmaking Collaborative Professor</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Art &amp; Design</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>bmadsen@mgsa.rutgers.edu</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.masongross.rutgers.edu/degrees-programs/art-design/faculty-staff/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Rutgers University, Mason Gross School of the Arts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mark Armijo McKnight</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Expanded Photography</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Art &amp; Design</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>mark.mcknight@rutgers.edu</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.masongross.rutgers.edu/degrees-programs/art-design/faculty-staff/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rutgers University, Mason Gross School of the Arts</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jeanine Oleson</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Associate Professor, Sculpture Graduate Director, Visual Arts</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Art &amp; Design</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>jeanine.oleson@rutgers.edu</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.masongross.rutgers.edu/degrees-programs/art-design/faculty-staff/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Rutgers University, Mason Gross School of the Arts</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rhys Bambrick</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Visual Arts Coordinator, Sculpture</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Art &amp; Design</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>rhys.bambrick@rutgers.edu</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.masongross.rutgers.edu/degrees-programs/art-design/faculty-staff/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rutgers University, Mason Gross School of the Arts</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sean Zujkowski</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Photo Area Coordinator</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Art &amp; Design</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>sdz18@mgsa.rutgers.edu</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.masongross.rutgers.edu/degrees-programs/art-design/faculty-staff/</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: United States</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: Ithaca, NY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: Cornell University, Department of Art (AAP) - /art/art-people listing (41 entries, 5 duplicates from dual program listings, deduped to 36 unique profiles) with emails only on individual profile pages - required a click-through pass like Ohio State. Medium classified from title/role text first, falling back to each profile's bio paragraph when the role alone was generic (e.g. 'Professor'). 5 rows have email_type=department_general: several visiting/affiliated faculty list the shared imagetext@cornell.edu program mailbox as their own contact on their profile page, not a personal address - flagged rather than treated as equivalent to a direct personal email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://aap.cornell.edu/art/art-people (plus 36 individual /people/&lt;slug&gt;/ pages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Paul Ramírez Jonas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Chair</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>par237@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/paul-ramirez-jonas/</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Keith Obadike</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Director of Undergraduate Studies</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>kao83@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/keith-obadike/</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Joanna Malinowska</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Director of Graduate Studies in Creative Visual Arts</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>jmm828@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/joanna-malinowska/</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nicholas Muellner</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Codirector, M.F.A. in Image Text and ITI Press</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>nrm72@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/nicholas-muellner/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Catherine Taylor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Codirector, M.F.A. in Image Text and ITI Press</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>cct29@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/catherine-taylor/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Lou Fuchs</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sculpture Studio Technician</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>lff37@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/lou-fuchs/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jackie Riccio</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Print Media, Drawing, and Painting Studio Technician</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>jr2452@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/jackie-riccio/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jennifer Gioffre Todd</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Director of Material Practice</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>jmg393@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/jennifer-gioffre-todd/</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Michael Ashkin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ma352@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/michael-ashkin/</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Oscar Rene Cornejo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>orc7@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/oscar-rene-cornejo/</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Jen de los Reyes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>jd2276@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/jen-de-los-reyes/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Leeza Meksin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>evm28@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/leeza-meksin/</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Elisabeth Meyer</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ehm2@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/elisabeth-meyer/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Carl Ostendarp</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>cao24@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/carl-ostendarp/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Maria Park</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>myp4@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/maria-park/</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Leslie Brack</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>lb624@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/leslie-brack/</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Carla Liesching</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>cel242@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/carla-liesching/</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Matt Bollinger</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Visiting Critic</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>mlb522@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/matt-bollinger/</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mark Anthony Brown Jr.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Strauch Early Career Fellow</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>mab692@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/mark-anthony-brown-jr/</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Matthew Connors</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Visiting Critic (summer 2026)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>imagetext@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>department_general</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/matthew-connors/</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Claire Donato</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Visiting Critic (summer and fall 2026)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>imagetext@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>department_general</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/claire-donato/</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Whitney Hubbs</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Visiting Critic (summer and fall 2026)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>weh62@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/whitney-hubbs/</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kyle Bellucci Johanson</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Visiting Critic</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>kj368@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/kyle-bellucci-johanson/</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ben Rivers</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Visiting Critic (summer 2026)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>imagetext@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>department_general</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/ben-rivers/</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Keisha Scarville</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Visiting Critic (fall 2026)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>imagetext@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>department_general</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/keisha-scarville/</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Paulina Velázquez Solís</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Visiting Critic</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>pv233@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/paulina-velazquez-solis/</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Carla Williams</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Visiting Critic (summer 2026)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>imagetext@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>department_general</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/carla-williams/</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Cornell University, Department of Art (AAP)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Carmen Winant</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Visiting Critic (summer 2026)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>cw297@cornell.edu</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://aap.cornell.edu/people/carmen-winant/</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I35"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Dezi Art Prize Faculty Scraping/master_faculty.xlsx
+++ b/Dezi Art Prize Faculty Scraping/master_faculty.xlsx
@@ -21,6 +21,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UIC" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutgers" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cornell" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Syracuse" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slade" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Temple-Tyler'!$A$7:$I$58</definedName>
@@ -37,6 +39,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'UIC'!$A$7:$I$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Rutgers'!$A$7:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Cornell'!$A$7:$I$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Syracuse'!$A$7:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Slade'!$A$7:$I$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6404,6 +6408,1397 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: United States</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: Syracuse, NY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: Syracuse University, College of Visual and Performing Arts, School of Art - /academics/art/contact/ page (the master faculty-staff directory is a JS search widget with no default results, confirmed unusable per the brief). This page has the School of Art Director (medium classified from bio text on his own profile page - no discipline given on the contact page for this role) plus 4 'Area Leads' with a discipline label given directly (e.g. 'Printmaking', 'Illustration B.F.A.') but email only on their individual profile page. 1 area lead (Studio Arts B.F.A./B.S., generalist label with no specific medium) excluded rather than guessed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://vpa.syracuse.edu/academics/art/contact/ (plus 4 individual /faculty-staff/&lt;slug&gt;/ profile pages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Syracuse University, College of Visual and Performing Arts, School of Art</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Professor Robert Wysocki</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>School of Art Director</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>School of Art</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>rjwysock@syr.edu</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://vpa.syracuse.edu/academics/art/contact/</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Syracuse University, College of Visual and Performing Arts, School of Art</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Frank Cammuso</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Area Lead, Illustration B.F.A.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Illustration B.F.A.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>fvcammus@syr.edu</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://vpa.syracuse.edu/faculty-staff/cammuso-frank/</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Syracuse University, College of Visual and Performing Arts, School of Art</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dusty Herbig</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Area Lead, Printmaking</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Printmaking</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>dtherbig@syr.edu</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://vpa.syracuse.edu/faculty-staff/herbig-dusty-1/</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Syracuse University, College of Visual and Performing Arts, School of Art</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ekaterina Vanovskaya</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Area Lead, Drawing and Painting</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Drawing and Painting</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>evanovsk@syr.edu</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://vpa.syracuse.edu/faculty-staff/vanovskaya-ekaterina-1/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: London, England</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: Slade School of Fine Art, University College London (UCL) - /people/academic/ listing (46 people, single page, no pagination). Medium classified from title text shown directly on the listing (e.g. 'Lecturer, Painting', 'Associate Professor, Sculpture'); email only on individual profile pages - required a click-through pass for the 21 in-scope people.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://www.ucl.ac.uk/slade/people/academic/ (plus 21 individual profile pages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kate Bright</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Associate Professor, Head of Undergraduate Sculpture (spring and summer terms 2024)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>k.bright@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/kbrig40/</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Peter Davies</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Lecturer, Painting</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>peter.davies@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/pdavi97/</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jade de Montserrat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Lecturer, Painting</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>j.montserrat@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/jdemo02/</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Lilah Fowler</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Associate Professor, Sculpture</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>l.fowler@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/lmfow09/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nadia Hebson</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Associate Professor, Co-Director of Studies, Graduate Programmes, Head of Graduate Painting, Graduate Tutor (MA/MFA)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>n.hebson@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/njheb06/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Holly Hendry</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Lecturer, Sculpture</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>holly.hendry.09@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/hhend03/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Neil Jeffries</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Lecturer, Painting</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>n.jeffries@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/nfjef05/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Christine Kirubi</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lecturer, Painting</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>christine.kirubi@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/cmkir12/</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Brighid Lowe</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Professor of Fine Art, Sculpture</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>b.lowe@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/blowe96/</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Onya McCausland</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Associate Professor, Head of Undergraduate Painting</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>o.mccausland@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/omcca29/</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hayley Newman</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Associate Professor, Sculpture</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>h.newman@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/hjene78/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Katrina Palmer</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Professor of Fine Art, Sculpture</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>katrina.palmer@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/kpalm97/</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Liz Rideal</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Professor of Fine Art, Painting</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>l.rideal@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/mecri22/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Karin Ruggaber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Professor of Fine Art, Head of Graduate Sculpture</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>k.ruggaber@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/krugg33/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Adam Saad</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Lecturer, Painting</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>adam.saad@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/asaad11/</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Zeinab Saleh</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Lecturer, Painting</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>zeinab.saleh@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/zsale90/</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Gary Stevens</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Associate Professor, Sculpture</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>g.stevens@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/gstev52/</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Jack Strange</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Lecturer, Sculpture</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>jack.strange@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/jtdst45/</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Estelle Thompson</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Professor, Painting</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>estelle.thompson@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/ethom85/</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Phoebe Unwin</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Associate Professor, Painting</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>phoebe.unwin@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/pcunw18/</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art, University College London (UCL)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Jo Volley</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Associate Professor, Painting</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Slade School of Fine Art</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>j.volley@ucl.ac.uk</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.ucl.ac.uk/slade/people/academic/jvoll94/</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I28"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Dezi Art Prize Faculty Scraping/master_faculty.xlsx
+++ b/Dezi Art Prize Faculty Scraping/master_faculty.xlsx
@@ -23,6 +23,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cornell" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Syracuse" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slade" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CMU" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSA" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kunstakademie Dusseldorf" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Temple-Tyler'!$A$7:$I$58</definedName>
@@ -41,6 +45,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Cornell'!$A$7:$I$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Syracuse'!$A$7:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Slade'!$A$7:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Yale'!$A$7:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'CMU'!$A$7:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'GSA'!$A$7:$I$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Kunstakademie Dusseldorf'!$A$7:$I$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7799,6 +7807,2509 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: United States</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: New Haven, CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: Yale School of Art - the brief correctly found the /about/people/faculty-and-staff listing page has no emails, classifying Yale as Tier 3. However each of the 74 people listed (Academic Leadership, Graphic Design, Painting/Printmaking, Photography, Sculpture, Interdepartmental, Undergraduate, Yale Norfolk, Faculty Emeriti sections; Faculty Governing Board and Administration/Staff excluded) links to their own profile page, and SOME publish a direct email there (appears to be individual choice - several senior faculty link to a personal site/Substack instead). Only 6 of 49 in-scope profiles checked had a public email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://www.art.yale.edu/about/people/faculty-and-staff (plus 49 individual /&lt;Name&gt; profile pages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Yale School of Art</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Anoka Faruqee</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Associate Dean; Professor in Painting/Printmaking</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>academic leadership</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>anoka.faruqee@yale.edu</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.art.yale.edu/AnokaFaruqee</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Yale School of Art</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Yeju Choi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Senior Critic</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>graphic design</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>yeju.choi@yale.edu</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.art.yale.edu/YejuChoi</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Yale School of Art</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Anahita Vossoughi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Critic; Associate Director of Digital Media</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>painting / printmaking</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>anahita.vossoughi@yale.edu</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.art.yale.edu/AnahitaVossoughi</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Yale School of Art</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sam Contis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Senior Critic</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>photography</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>sam.contis@yale.edu</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.art.yale.edu/SamContis</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Yale School of Art</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Matthew Leifheit</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Critic</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>photography</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>leifheit.matthew@gmail.com</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.art.yale.edu/MatthewLeifheit</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Yale School of Art</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Eva O'Leary</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Critic</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>photography</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>eva.oleary@yale.edu</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.art.yale.edu/EvaOLeary</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: United States</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: Pittsburgh, PA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: Carnegie Mellon University, School of Art - the brief's warning ("directory requires Andrew login, do NOT scrape") correctly applies to CMU's university-wide people directory, which was NOT used here. This is a different, fully public page - art.cmu.edu/people/faculty/ - the School of Art's own faculty listing, not login-walled. Individual profile pages publish a real institutional email (@andrew.cmu.edu or @cmu.edu) in a structured JSON metadata field. Medium classified from the discipline label shown directly on the listing (e.g. 'Drawing, Painting, Print, &amp; Photo', 'Electronic &amp; Time Based Media' - the latter mapped to Filmmaking as the closest of the 9 in-scope mediums, though it also covers interactive/digital work; an approximate call).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://art.cmu.edu/people/faculty/ (plus 14 individual /people/&lt;slug&gt;/ pages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University, School of Art</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kim Beck</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Professor of Art</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Drawing, Painting, Print, &amp; Photo</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>kimbeck@andrew.cmu.edu</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://art.cmu.edu/people/kim-beck/</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University, School of Art</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Meghana Bisineer</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Electronic &amp; Time Based Media</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>mbisinee@andrew.cmu.edu</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://art.cmu.edu/people/meghana-bisineer/</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University, School of Art</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Johannes DeYoung</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Associate Professor of Art</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Electronic &amp; Time Based Media</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>jsdeyoung@cmu.edu</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://art.cmu.edu/people/johannes-deyoung/</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University, School of Art</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Isla Hansen</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Art</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sculpture, Installation, &amp; Site Work</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ihansen@andrew.cmu.edu</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://art.cmu.edu/people/isla-hansen/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University, School of Art</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sujin Kim</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Associate Professor of Art</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Electronic &amp; Time Based Media</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>kimsujin@cmu.edu</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://art.cmu.edu/people/sujin-kim/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University, School of Art</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Golan Levin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Professor of Art</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Electronic &amp; Time Based Media</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>golan@andrew.cmu.edu</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://art.cmu.edu/people/golan-levin/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University, School of Art</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Clayton Merrell</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dorothy L. Stubnitz Professor of Art</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Drawing, Painting, Print, &amp; Photo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>cmerrell@andrew.cmu.edu</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://art.cmu.edu/people/clayton-merrell/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University, School of Art</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Paolo Pedercini</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Associate Professor of Art</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Electronic &amp; Time Based Media</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>paolop@cmu.edu</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://art.cmu.edu/people/paolo-pedercini/</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University, School of Art</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rich Pell</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Associate Professor of Art</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Electronic &amp; Time Based Media</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>rp3h@andrew.cmu.edu</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://art.cmu.edu/people/rich-pell/</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University, School of Art</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Britt Ransom</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Associate Professor of Art</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Sculpture, Installation, &amp; Site Work</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>brittanr@andrew.cmu.edu</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://art.cmu.edu/people/britt-ransom/</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University, School of Art</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sharmistha Ray</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Estella Loomis McCandless Assistant Professor of Art</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Drawing, Painting, Print, &amp; Photo</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>sharmisr@andrew.cmu.edu</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://art.cmu.edu/people/sharmistha-ray/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University, School of Art</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Yoko Sekino-Bové</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Assistant Teaching Professor of Art</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sculpture, Installation, &amp; Site Work</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ysekinob@andrew.cmu.edu</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://art.cmu.edu/people/yoko-sekino-bove/</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University, School of Art</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jamie Wolfe</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Art</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Electronic &amp; Time Based Media</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>jamiewol@andrew.cmu.edu</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://art.cmu.edu/people/jamie-wolfe/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University, School of Art</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Imin Yeh</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Drawing, Painting, Print, &amp; Photo</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>iminyeh@cmu.edu</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://art.cmu.edu/people/imin-yeh/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I21"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: Glasgow, Scotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: Glasgow School of Art - the brief correctly found the /staff listing page has no emails, classifying GSA as Tier 3. However individual profile pages DO publish a real email (e.g. 'Email: N.Oddy@gsa.ac.uk') even though the listing itself doesn't show it. ~197 total staff across all departments (architecture, design history, admin, etc., 2 pages); medium classified from job title text, keeping only the ~29 whose title names an in-scope medium (e.g. 'Lecturer in Painting and Printmaking', 'Lecturer Sculpture and Environmental Art').</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://www.gsa.ac.uk/staff (2 pages, plus ~29 individual /staff/user-&lt;id&gt; pages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aoife McGarrigle</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pathway Tutor M.Litt Print Media, Lithography technician, Team Leader TSD Print</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fiber and Material Arts</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>A.McGarrigle@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-230</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Annette Heyer</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Lecturer in Painting and Printmaking</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>A.Heyer@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-231</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Justin Carter</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Lecturer in Sculpture &amp; Environmental Art</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>J.Carter@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-239</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Peter McCaughey</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Lecturer Sculpture and Environmental Art</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>P.McCaughey@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-240</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Christina McBride</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Lecturer Master of Fine Art (MFA) and Fine Art Photography</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>C.McBride@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-253</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Lesley Punton</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Head of Fine Art Photography</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>L.Punton@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-281</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Anna Gordon</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>head of department and programme leader, silversmithing and jewellery</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>A.Gordon@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-284</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ronan Breslin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lecturer Sound for the Moving Image</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>R.Breslin@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-316</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Eddie Stewart</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Lecturer Painting &amp; Printmaking</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ed.Stewart@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-395</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stephanie Smith</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Lecturer Sculpture Environmental Art / PhD Primary &amp; Secondary Supervisor</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S.Smith@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-401</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dr Graham Lister</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Lecturer - Painting and Printmaking</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>G.Lister@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-412</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Michael Mersinis</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Lecturer in Fine Art Photography</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>M.Mersinis@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-448</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chris Wallace</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>P/T Lecturer Product Design Engineering</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>C.Wallace@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-656</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Paul Maguire</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Programme Leader, BA (Hons) Interaction Design</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>P.Maguire@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-722</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kirsty Ross</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Lecturer and Final Year Coordinator, Department of Product Design, the Innovation School</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>K.Ross@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-754</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fiona Ann Jardine</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Programme Leader, Fashion Narrative</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>F.Jardine@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-925</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dr Michael Stubbs</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Reader in Contemporary Painting</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>M.Stubbs@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-1024</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Chris Hand</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Lecturer and subject lead for Interaction Design</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>C.Hand@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-1061</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Jessica Argo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Programme Leader, BDes Sound for Moving Image</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Filmmaking</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>J.Argo@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-1072</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Marianne Anderson</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Lecturer, Silversmithing &amp; Jewellery</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>M.Anderson@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-1162</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Becky Šik</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Lecturer in Sculpture and Environmental Art</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>B.Sik@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-1271</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Anne-Marie Copestake</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Lecturer Fine Art Photography</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>A.Copestake@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-1420</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sara Barker</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Head of Sculpture and Environmental Art</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S.Barker@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-1469</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dr Zoe Mendelson</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Head of Painting &amp; Printmaking</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>z.mendelson@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-1584</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Marita Fraser</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>UG Programme Director and Interim Head of Sculpture and Environmental Art,</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>m.fraser@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-1613</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Owain McGilvary</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Lecturer in Painting &amp; Printmaking</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>O.McGilvary@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-1658</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Rachel Adams</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Lecturer in Sculpture and Environmental Art</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>R.Adams@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-1679</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Karen David</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Lecturer in Painting &amp; Printmaking</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Painting/Drawing</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>k.david@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-1686</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Glasgow School of Art</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Matthew Williams</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Photography Lecturer</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>m.williams@gsa.ac.uk</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.gsa.ac.uk/staff/user-1848</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I36"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -10343,6 +12854,161 @@
     </row>
   </sheetData>
   <autoFilter ref="A7:I59"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country: Germany</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>City: Dusseldorf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Source: Kunstakademie Dusseldorf - the brief's Tier 3 classification (no emails, use postmaster@) is correct for the vast majority: checked all 24 'Freie Kunst' (Free Art) professors' individual profile pages (JS-rendered, required crawl4ai) and only 1 (Alexandra Bircken) publishes an email, included in her application-instructions text ('send your portfolio to alexandra.bircken@kunstakademie-duesseldorf.de'). The other 23 genuinely have no email anywhere on their page, confirmed by direct inspection, not a fetch failure. Baukunst (Architecture) and Kunstbezogene Wissenschaften (art theory/sciences) sections excluded as out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://kunstakademie-duesseldorf.de/studienangebot-und-bewerbung/professor-innen/ (plus 24 individual profile pages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>school_name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>faculty_name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>email_type</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>date_extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kunstakademie Dusseldorf (Dusseldorf Art Academy)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Prof.in Alexandra Bircken</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Professor, Freie Kunst</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Freie Kunst</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sculpture</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>alexandra.bircken@kunstakademie-duesseldorf.de</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://kunstakademie-duesseldorf.de/studienangebot-und-bewerbung/professor-innen/prof-in-alexandra-bircken/</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:I8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
